--- a/CURSO_3_PY_ML/graficos matplotlib seaborn.xlsx
+++ b/CURSO_3_PY_ML/graficos matplotlib seaborn.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\PYTHON\cursos-PYTHON\CURSO_3_PY_ML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39FA52C9-99A5-45C4-A100-A483368419B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8FA578-416F-4945-BB46-4B9166A855B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="108">
   <si>
     <t>Gráfico</t>
   </si>
@@ -755,17 +755,33 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>pairplot</t>
+  </si>
+  <si>
+    <t>Multi-Grafico</t>
+  </si>
+  <si>
+    <t>displot</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -808,7 +824,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -821,8 +837,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -845,36 +873,64 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1094,282 +1150,282 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
     <col min="2" max="2" width="31.5703125" customWidth="1"/>
-    <col min="3" max="3" width="37.5703125" customWidth="1"/>
-    <col min="4" max="4" width="62.85546875" customWidth="1"/>
+    <col min="3" max="3" width="41" customWidth="1"/>
+    <col min="4" max="4" width="67.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>70</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="4" t="s">
         <v>72</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="4" t="s">
         <v>74</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="4" t="s">
         <v>78</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="4" t="s">
         <v>80</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="4" t="s">
         <v>83</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="16" t="s">
         <v>85</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="11" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="7" t="s">
         <v>49</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="7" t="s">
         <v>52</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="7" t="s">
         <v>55</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="7" t="s">
         <v>58</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="7" t="s">
         <v>61</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="7" t="s">
         <v>64</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="7" t="s">
         <v>67</v>
       </c>
       <c r="E18" s="2"/>
@@ -1379,164 +1435,176 @@
       <c r="B19" s="3"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C33" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
